--- a/data/trans_orig/P16A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>28775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485791</t>
+          <t>486681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493214</t>
+          <t>493221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437746</t>
+          <t>438714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>455208</t>
+          <t>455657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>928941</t>
+          <t>929049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>947976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>41433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723595</t>
+          <t>723672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733567</t>
+          <t>732841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584201</t>
+          <t>584061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605272</t>
+          <t>606069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1312272</t>
+          <t>1314075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1336913</t>
+          <t>1336887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614267</t>
+          <t>614659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630410</t>
+          <t>631026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656872</t>
+          <t>656639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>675558</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277878</t>
+          <t>1278307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302139</t>
+          <t>1301759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502227</t>
+          <t>501820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515186</t>
+          <t>515141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483521</t>
+          <t>483789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502047</t>
+          <t>502875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994044</t>
+          <t>992566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014620</t>
+          <t>1014016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365728</t>
+          <t>365162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>381009</t>
+          <t>380423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365029</t>
+          <t>364846</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385183</t>
+          <t>385664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>734634</t>
+          <t>737960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>761509</t>
+          <t>761797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>48995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61414</t>
+          <t>65550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271424</t>
+          <t>271197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286280</t>
+          <t>286176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293630</t>
+          <t>293939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316222</t>
+          <t>315596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>574103</t>
+          <t>569967</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>598832</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>28940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56697</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180671</t>
+          <t>180943</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199181</t>
+          <t>199618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298242</t>
+          <t>297679</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318273</t>
+          <t>318846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487094</t>
+          <t>488222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>512897</t>
+          <t>513930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>94985</t>
+          <t>91669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204663</t>
+          <t>206254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>222735</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>281987</t>
+          <t>286084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3180540</t>
+          <t>3183856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3216910</t>
+          <t>3218135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3174534</t>
+          <t>3172943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3225050</t>
+          <t>3224525</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6372735</t>
+          <t>6368638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6434293</t>
+          <t>6431987</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443936</t>
+          <t>443338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452146</t>
+          <t>452080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412526</t>
+          <t>413247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>425362</t>
+          <t>424442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861447</t>
+          <t>861199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>875478</t>
+          <t>874626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>58795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>668025</t>
+          <t>668057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681609</t>
+          <t>682277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>562002</t>
+          <t>561286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>585899</t>
+          <t>586027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1237486</t>
+          <t>1236656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1264688</t>
+          <t>1263410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54341</t>
+          <t>55346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668985</t>
+          <t>667977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678245</t>
+          <t>678237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651594</t>
+          <t>650589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676732</t>
+          <t>676414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325506</t>
+          <t>1325511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1352717</t>
+          <t>1352440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40708</t>
+          <t>41990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602968</t>
+          <t>602708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612630</t>
+          <t>612614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571285</t>
+          <t>570003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>596040</t>
+          <t>593785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1179200</t>
+          <t>1178934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1204274</t>
+          <t>1204544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>420660</t>
+          <t>419839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428344</t>
+          <t>427527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409331</t>
+          <t>409891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430200</t>
+          <t>430124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>834993</t>
+          <t>834884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>855593</t>
+          <t>856235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39927</t>
+          <t>41084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55800</t>
+          <t>55365</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>288315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302906</t>
+          <t>302737</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313132</t>
+          <t>311975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334986</t>
+          <t>334259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>605054</t>
+          <t>605489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633674</t>
+          <t>633229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>42492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74103</t>
+          <t>73653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229425</t>
+          <t>230103</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245724</t>
+          <t>245781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324641</t>
+          <t>325211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351284</t>
+          <t>351814</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561686</t>
+          <t>562136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>593315</t>
+          <t>593297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>185266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243332</t>
+          <t>243139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>227342</t>
+          <t>228931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>292577</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357597</t>
+          <t>3356818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3385115</t>
+          <t>3386499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3300762</t>
+          <t>3300955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3358794</t>
+          <t>3358828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6670705</t>
+          <t>6669232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6735940</t>
+          <t>6734351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414696</t>
+          <t>413803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376011</t>
+          <t>375806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389073</t>
+          <t>389283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>795377</t>
+          <t>793921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808633</t>
+          <t>808420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577934</t>
+          <t>577676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588523</t>
+          <t>588498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540280</t>
+          <t>540316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555240</t>
+          <t>554787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1122513</t>
+          <t>1123057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140753</t>
+          <t>1140660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658308</t>
+          <t>659768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668026</t>
+          <t>668045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>622138</t>
+          <t>621746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643511</t>
+          <t>642704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287543</t>
+          <t>1287073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309948</t>
+          <t>1309583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39339</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632210</t>
+          <t>631425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643856</t>
+          <t>643620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609738</t>
+          <t>609745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631829</t>
+          <t>631908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1249004</t>
+          <t>1250616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1272666</t>
+          <t>1272646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462303</t>
+          <t>461483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474765</t>
+          <t>475521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467558</t>
+          <t>465844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484704</t>
+          <t>484018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935997</t>
+          <t>934942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957336</t>
+          <t>957385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320336</t>
+          <t>320105</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331293</t>
+          <t>331363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>345078</t>
+          <t>344295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>363399</t>
+          <t>362864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>670932</t>
+          <t>670011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>693215</t>
+          <t>691556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239121</t>
+          <t>238415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251000</t>
+          <t>251035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360910</t>
+          <t>360261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383942</t>
+          <t>384582</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605691</t>
+          <t>606138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631979</t>
+          <t>630640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>58279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>122626</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172901</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162858</t>
+          <t>166431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218963</t>
+          <t>217995</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3335803</t>
+          <t>3336071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3362710</t>
+          <t>3361436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3371641</t>
+          <t>3369207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3420951</t>
+          <t>3421916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6719929</t>
+          <t>6720897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6776034</t>
+          <t>6772461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390301</t>
+          <t>391339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294196</t>
+          <t>296059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311582</t>
+          <t>311702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691349</t>
+          <t>692659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710451</t>
+          <t>710668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>26897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414866</t>
+          <t>413860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423381</t>
+          <t>423383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485413</t>
+          <t>487589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504607</t>
+          <t>505118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908632</t>
+          <t>908154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926090</t>
+          <t>927167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522377</t>
+          <t>522590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533434</t>
+          <t>534048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521507</t>
+          <t>520792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533620</t>
+          <t>532890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1048403</t>
+          <t>1048548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1064432</t>
+          <t>1064907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>29926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>67507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862414</t>
+          <t>861789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881963</t>
+          <t>882808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666493</t>
+          <t>666348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686670</t>
+          <t>686442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1535528</t>
+          <t>1533160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1570564</t>
+          <t>1570741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47547</t>
+          <t>48445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>71368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529276</t>
+          <t>527791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546237</t>
+          <t>545733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497340</t>
+          <t>496442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>514771</t>
+          <t>514904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1032534</t>
+          <t>1033756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1056466</t>
+          <t>1057826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53113</t>
+          <t>54048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349110</t>
+          <t>348944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360376</t>
+          <t>360664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>565205</t>
+          <t>565519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597697</t>
+          <t>596987</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>923420</t>
+          <t>922485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>955129</t>
+          <t>956094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55665</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46082</t>
+          <t>46413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67762</t>
+          <t>69023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>265940</t>
+          <t>266073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275854</t>
+          <t>275520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368729</t>
+          <t>367989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386213</t>
+          <t>386287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>638901</t>
+          <t>637640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>660581</t>
+          <t>660250</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148904</t>
+          <t>149245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206724</t>
+          <t>208661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>212144</t>
+          <t>215097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284391</t>
+          <t>282375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3372311</t>
+          <t>3370526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3407404</t>
+          <t>3406662</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3450978</t>
+          <t>3449041</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3508798</t>
+          <t>3508457</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6831641</t>
+          <t>6833657</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6903888</t>
+          <t>6900935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486681</t>
+          <t>486756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493221</t>
+          <t>493218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438714</t>
+          <t>438516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>455657</t>
+          <t>455563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929049</t>
+          <t>928648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947976</t>
+          <t>947314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19425</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723672</t>
+          <t>724128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732841</t>
+          <t>733547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584061</t>
+          <t>584700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606069</t>
+          <t>606189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1314075</t>
+          <t>1312928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1336887</t>
+          <t>1336870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>24053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>32208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614659</t>
+          <t>613596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631026</t>
+          <t>629807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656639</t>
+          <t>657536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>675991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1278307</t>
+          <t>1277742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1301759</t>
+          <t>1302213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501820</t>
+          <t>501514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515141</t>
+          <t>515296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483789</t>
+          <t>482860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502875</t>
+          <t>502187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992566</t>
+          <t>991675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014016</t>
+          <t>1014301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>55770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365162</t>
+          <t>364567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380423</t>
+          <t>380108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364846</t>
+          <t>365540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385664</t>
+          <t>384666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>737960</t>
+          <t>734926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>761797</t>
+          <t>761900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>48055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>37193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271197</t>
+          <t>271217</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286176</t>
+          <t>285645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293939</t>
+          <t>294879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315596</t>
+          <t>315968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569967</t>
+          <t>570038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>598199</t>
+          <t>598324</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>36213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29861</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>57339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180943</t>
+          <t>182938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199618</t>
+          <t>199627</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297679</t>
+          <t>297695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318846</t>
+          <t>318054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>488222</t>
+          <t>486452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513930</t>
+          <t>513639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91669</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>207030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222735</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>286084</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3183856</t>
+          <t>3181802</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3218135</t>
+          <t>3218616</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3172943</t>
+          <t>3172167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3224525</t>
+          <t>3226344</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6368638</t>
+          <t>6363966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6431987</t>
+          <t>6430450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443338</t>
+          <t>443191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452080</t>
+          <t>452098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413247</t>
+          <t>412236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424442</t>
+          <t>425203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861199</t>
+          <t>861343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>874626</t>
+          <t>875432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>668057</t>
+          <t>666910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682277</t>
+          <t>682354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561286</t>
+          <t>561780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>586027</t>
+          <t>586603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1236656</t>
+          <t>1237914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1263410</t>
+          <t>1265181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29521</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>34064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60478</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667977</t>
+          <t>669131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678237</t>
+          <t>678267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650589</t>
+          <t>650784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676414</t>
+          <t>677203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325511</t>
+          <t>1324095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1352440</t>
+          <t>1351925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41990</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>46607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602708</t>
+          <t>603031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612614</t>
+          <t>612538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570003</t>
+          <t>571476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593785</t>
+          <t>594701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1178934</t>
+          <t>1180003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1204544</t>
+          <t>1205575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19909</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>43173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419839</t>
+          <t>420278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427527</t>
+          <t>427531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409891</t>
+          <t>410358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430124</t>
+          <t>429713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>834884</t>
+          <t>832971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>856235</t>
+          <t>855633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288315</t>
+          <t>287797</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302737</t>
+          <t>302777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>311975</t>
+          <t>311986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334259</t>
+          <t>334498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>605489</t>
+          <t>608016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633229</t>
+          <t>633092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61542</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230103</t>
+          <t>229290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245781</t>
+          <t>245705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>324998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351814</t>
+          <t>350744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562136</t>
+          <t>564141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>593297</t>
+          <t>594470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185266</t>
+          <t>184917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243139</t>
+          <t>244436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228931</t>
+          <t>227027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294050</t>
+          <t>293901</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3356818</t>
+          <t>3356780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3386499</t>
+          <t>3387292</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3300955</t>
+          <t>3299658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3358828</t>
+          <t>3359177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6669232</t>
+          <t>6669381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6734351</t>
+          <t>6736255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413803</t>
+          <t>414763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375806</t>
+          <t>376211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389283</t>
+          <t>390020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>793921</t>
+          <t>794612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808420</t>
+          <t>808531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577676</t>
+          <t>578504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588498</t>
+          <t>588382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540316</t>
+          <t>540913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>554787</t>
+          <t>555226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123057</t>
+          <t>1122335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140660</t>
+          <t>1140166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43410</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659768</t>
+          <t>659089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668045</t>
+          <t>668051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>621746</t>
+          <t>622744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642704</t>
+          <t>642446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287073</t>
+          <t>1287191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309583</t>
+          <t>1309079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22479</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44509</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631425</t>
+          <t>631792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643620</t>
+          <t>643589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609745</t>
+          <t>610687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631908</t>
+          <t>632266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1250616</t>
+          <t>1248312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1272646</t>
+          <t>1272434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461483</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475521</t>
+          <t>474774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465844</t>
+          <t>466990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484018</t>
+          <t>485004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>934942</t>
+          <t>933507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957385</t>
+          <t>956773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>41762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320105</t>
+          <t>321308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331363</t>
+          <t>331405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344295</t>
+          <t>345558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>362864</t>
+          <t>363821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>670011</t>
+          <t>670330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>691556</t>
+          <t>692397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>38923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>51427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238415</t>
+          <t>239720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251035</t>
+          <t>251123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360261</t>
+          <t>361246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384582</t>
+          <t>384012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>606138</t>
+          <t>605740</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>630640</t>
+          <t>631801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122626</t>
+          <t>123306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175335</t>
+          <t>171513</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166431</t>
+          <t>165567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217995</t>
+          <t>219283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3336071</t>
+          <t>3337456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361436</t>
+          <t>3362290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3369207</t>
+          <t>3373029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3421916</t>
+          <t>3421236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6720897</t>
+          <t>6719609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6772461</t>
+          <t>6773325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398182</t>
+          <t>406138</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391339</t>
+          <t>399436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306472</t>
+          <t>353770</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296059</t>
+          <t>340820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311702</t>
+          <t>360107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>704654</t>
+          <t>759908</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692659</t>
+          <t>746889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710668</t>
+          <t>766904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421656</t>
+          <t>471066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413860</t>
+          <t>459274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423383</t>
+          <t>475318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>497695</t>
+          <t>485552</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487589</t>
+          <t>474992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505118</t>
+          <t>492156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>919351</t>
+          <t>956618</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908154</t>
+          <t>943239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927167</t>
+          <t>965317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,17 +10421,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529728</t>
+          <t>614083</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522590</t>
+          <t>607068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534048</t>
+          <t>618378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>528205</t>
+          <t>604898</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520792</t>
+          <t>596473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532890</t>
+          <t>610331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1057933</t>
+          <t>1218980</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1048548</t>
+          <t>1209450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1064907</t>
+          <t>1226951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67507</t>
+          <t>65788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>873513</t>
+          <t>684849</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861789</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882808</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677183</t>
+          <t>699139</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666348</t>
+          <t>688941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686442</t>
+          <t>707428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1550697</t>
+          <t>1383989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1533160</t>
+          <t>1371716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1570741</t>
+          <t>1395902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>30783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>63861</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47298</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71368</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>538720</t>
+          <t>586961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>527791</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545733</t>
+          <t>594635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>507021</t>
+          <t>564984</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>496442</t>
+          <t>555386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>514904</t>
+          <t>574971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1045741</t>
+          <t>1151946</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033756</t>
+          <t>1137646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1057826</t>
+          <t>1163621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>37282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54048</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>355777</t>
+          <t>393588</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348944</t>
+          <t>385982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360664</t>
+          <t>398599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>582200</t>
+          <t>410029</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>565519</t>
+          <t>401884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596987</t>
+          <t>417293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>937977</t>
+          <t>803617</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>922485</t>
+          <t>793041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956094</t>
+          <t>812224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56405</t>
+          <t>59899</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69023</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>271877</t>
+          <t>297554</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>291361</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275520</t>
+          <t>301782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>377757</t>
+          <t>413806</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367989</t>
+          <t>403180</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386287</t>
+          <t>422593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>649634</t>
+          <t>711360</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>637640</t>
+          <t>698614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>660250</t>
+          <t>722177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>178432</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208661</t>
+          <t>226139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>215097</t>
+          <t>249208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282375</t>
+          <t>307629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3389454</t>
+          <t>3454239</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370526</t>
+          <t>3437344</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3406662</t>
+          <t>3471088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3476533</t>
+          <t>3532179</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3449041</t>
+          <t>3506174</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3508457</t>
+          <t>3553881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6865987</t>
+          <t>6986418</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6833657</t>
+          <t>6955964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6900935</t>
+          <t>7014385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
